--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_magallanes.xlsx
@@ -54,18 +54,18 @@
     <t xml:space="preserve">Torres del Paine</t>
   </si>
   <si>
+    <t xml:space="preserve">Porvenir</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Gregorio</t>
   </si>
   <si>
-    <t xml:space="preserve">Porvenir</t>
+    <t xml:space="preserve">Timaukel</t>
   </si>
   <si>
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
-    <t xml:space="preserve">Timaukel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:15</t>
+    <t xml:space="preserve">2026-09-10 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -599,7 +599,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>12104</v>
+        <v>12301</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -612,7 +612,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>12301</v>
+        <v>12104</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -625,7 +625,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>12201</v>
+        <v>12303</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -638,7 +638,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12303</v>
+        <v>12201</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2021_magallanes.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2021_magallanes.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:20</t>
+    <t xml:space="preserve">2026-09-18 10:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
